--- a/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
@@ -72,8 +72,15 @@
     <numFmt numFmtId="177" formatCode="yyyy-MM-dd"/>
     <numFmt numFmtId="178" formatCode="yyyy-MM-dd HH:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -108,8 +115,9 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -516,62 +524,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>43831.427141203705</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>43831</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="b">
+      <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$3</definedName>

--- a/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
@@ -523,7 +523,7 @@
     <col min="6" max="6" width="9.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14" customHeight="1">
+    <row r="1" spans="1:6" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,7 +543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14" customHeight="1">
+    <row r="2" spans="1:6" ht="16" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14" customHeight="1">
+    <row r="3" spans="1:6" ht="16" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/NullableTests.NullDisplayShortcuts.verified.xlsx
@@ -523,7 +523,7 @@
     <col min="6" max="6" width="9.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" customHeight="1">
+    <row r="1" spans="1:6" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,7 +543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16" customHeight="1">
+    <row r="2" spans="1:6" ht="14" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16" customHeight="1">
+    <row r="3" spans="1:6" ht="14" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
